--- a/assets/dp.xlsx
+++ b/assets/dp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ubuntu\Github\blog\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4A3137-A03F-4B83-974A-7363415035A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9525B1B1-6436-49DC-867E-325A09C42EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{A5E86A53-B969-4D05-A10D-A2EA7885FEB1}"/>
   </bookViews>
